--- a/output/topology_excel/4738.xlsx
+++ b/output/topology_excel/4738.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,15 +784,15 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>363</v>
+        <v>97</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
         <v>5</v>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>115</v>
+        <v>365</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>365</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,18 +916,18 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>115</v>
+        <v>371</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="F23" t="n">
-        <v>140</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="n">
         <v>8</v>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="F27" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1048,10 +1048,54 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
+        <v>115</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
         <v>167</v>
       </c>
-      <c r="F28" t="n">
-        <v>13</v>
+      <c r="F29" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>366</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/4738.xlsx
+++ b/output/topology_excel/4738.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>118</v>
@@ -1007,7 +1007,7 @@
         <v>175</v>
       </c>
       <c r="F26" t="n">
-        <v>140</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
